--- a/artfynd/A 14058-2023 artfynd.xlsx
+++ b/artfynd/A 14058-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14058-2023 artfynd.xlsx
+++ b/artfynd/A 14058-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2255,6 +2255,327 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128315499</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78696</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>353</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Svartåsvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>417746</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6899734</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128315500</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92259</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Svartåsvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>417771</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6899716</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128315498</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79647</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Svartåsvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>417749</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6899736</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14058-2023 artfynd.xlsx
+++ b/artfynd/A 14058-2023 artfynd.xlsx
@@ -2261,7 +2261,7 @@
         <v>128315499</v>
       </c>
       <c r="B15" t="n">
-        <v>78696</v>
+        <v>78699</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>128315500</v>
       </c>
       <c r="B16" t="n">
-        <v>92259</v>
+        <v>92267</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>128315498</v>
       </c>
       <c r="B17" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 14058-2023 artfynd.xlsx
+++ b/artfynd/A 14058-2023 artfynd.xlsx
@@ -2261,7 +2261,7 @@
         <v>128315499</v>
       </c>
       <c r="B15" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>128315500</v>
       </c>
       <c r="B16" t="n">
-        <v>92267</v>
+        <v>92359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>128315498</v>
       </c>
       <c r="B17" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 14058-2023 artfynd.xlsx
+++ b/artfynd/A 14058-2023 artfynd.xlsx
@@ -2261,7 +2261,7 @@
         <v>128315499</v>
       </c>
       <c r="B15" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>128315500</v>
       </c>
       <c r="B16" t="n">
-        <v>92359</v>
+        <v>92371</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>128315498</v>
       </c>
       <c r="B17" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 14058-2023 artfynd.xlsx
+++ b/artfynd/A 14058-2023 artfynd.xlsx
@@ -2261,7 +2261,7 @@
         <v>128315499</v>
       </c>
       <c r="B15" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>128315500</v>
       </c>
       <c r="B16" t="n">
-        <v>92371</v>
+        <v>92373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>128315498</v>
       </c>
       <c r="B17" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 14058-2023 artfynd.xlsx
+++ b/artfynd/A 14058-2023 artfynd.xlsx
@@ -2368,7 +2368,7 @@
         <v>128315500</v>
       </c>
       <c r="B16" t="n">
-        <v>92373</v>
+        <v>92374</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 14058-2023 artfynd.xlsx
+++ b/artfynd/A 14058-2023 artfynd.xlsx
@@ -2261,7 +2261,7 @@
         <v>128315499</v>
       </c>
       <c r="B15" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>128315500</v>
       </c>
       <c r="B16" t="n">
-        <v>92374</v>
+        <v>92401</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>128315498</v>
       </c>
       <c r="B17" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 14058-2023 artfynd.xlsx
+++ b/artfynd/A 14058-2023 artfynd.xlsx
@@ -2261,7 +2261,7 @@
         <v>128315499</v>
       </c>
       <c r="B15" t="n">
-        <v>78782</v>
+        <v>78786</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>128315500</v>
       </c>
       <c r="B16" t="n">
-        <v>92401</v>
+        <v>92411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>128315498</v>
       </c>
       <c r="B17" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 14058-2023 artfynd.xlsx
+++ b/artfynd/A 14058-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>678658</v>
+        <v>129030</v>
       </c>
       <c r="B2" t="n">
-        <v>90840</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>417920.9596312334</v>
+        <v>418162</v>
       </c>
       <c r="R2" t="n">
-        <v>6899203.525493366</v>
+        <v>6899027</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2008-05-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-05-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olli Manninen, Eva Ydrén, Elina Hinkkanen, * Naturskyddare, Päivi Mattila</t>
+          <t>Olli Manninen, Päivi Mattila, Elina Hinkkanen, Eva Ydrén, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -801,53 +786,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>480417</v>
+        <v>128315499</v>
       </c>
       <c r="B3" t="n">
-        <v>89544</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hovdhållan, Hjd</t>
+          <t>Svartåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>418065.310534973</v>
+        <v>417746</v>
       </c>
       <c r="R3" t="n">
-        <v>6899085.671718287</v>
+        <v>6899734</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2008-05-22</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2008-05-22</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,45 +877,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Olli Manninen</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olli Manninen, Eva Ydrén, Elina Hinkkanen, * Naturskyddare, Päivi Mattila</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Naturskyddare</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>480001</v>
+        <v>479998</v>
       </c>
       <c r="B4" t="n">
-        <v>89544</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418044.9040604976</v>
+        <v>418060</v>
       </c>
       <c r="R4" t="n">
-        <v>6899111.369696621</v>
+        <v>6899090</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1000,19 +961,9 @@
           <t>2008-05-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-05-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,7 +993,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olli Manninen, * Naturskyddare, Päivi Mattila, Elina Hinkkanen, Eva Ydrén</t>
+          <t>Olli Manninen, Eva Ydrén, Elina Hinkkanen, * Naturskyddare, Päivi Mattila</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1053,37 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>678651</v>
+        <v>480001</v>
       </c>
       <c r="B5" t="n">
-        <v>90840</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1093,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418008.7544582126</v>
+        <v>418045</v>
       </c>
       <c r="R5" t="n">
-        <v>6899123.917003755</v>
+        <v>6899111</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1126,19 +1072,9 @@
           <t>2008-05-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2008-05-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,7 +1104,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olli Manninen, Päivi Mattila, Eva Ydrén, * Naturskyddare, Elina Hinkkanen</t>
+          <t>Olli Manninen, * Naturskyddare, Päivi Mattila, Elina Hinkkanen, Eva Ydrén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1179,15 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>480004</v>
+        <v>480003</v>
       </c>
       <c r="B6" t="n">
-        <v>89544</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>417996.4495929288</v>
+        <v>418032</v>
       </c>
       <c r="R6" t="n">
-        <v>6899136.81722755</v>
+        <v>6899132</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1252,19 +1183,9 @@
           <t>2008-05-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2008-05-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,7 +1215,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olli Manninen, Elina Hinkkanen, Eva Ydrén, * Naturskyddare, Päivi Mattila</t>
+          <t>Olli Manninen, * Naturskyddare, Elina Hinkkanen, Eva Ydrén, Päivi Mattila</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1305,15 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>480003</v>
+        <v>480004</v>
       </c>
       <c r="B7" t="n">
-        <v>89544</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418031.8578473004</v>
+        <v>417996</v>
       </c>
       <c r="R7" t="n">
-        <v>6899132.22156495</v>
+        <v>6899137</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1378,19 +1294,9 @@
           <t>2008-05-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2008-05-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,7 +1326,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olli Manninen, * Naturskyddare, Elina Hinkkanen, Eva Ydrén, Päivi Mattila</t>
+          <t>Olli Manninen, Elina Hinkkanen, Eva Ydrén, * Naturskyddare, Päivi Mattila</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1431,15 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>479998</v>
+        <v>480412</v>
       </c>
       <c r="B8" t="n">
-        <v>89544</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418060.2632349356</v>
+        <v>418162</v>
       </c>
       <c r="R8" t="n">
-        <v>6899089.528086353</v>
+        <v>6899027</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1504,19 +1405,9 @@
           <t>2008-05-22</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2008-05-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1546,7 +1437,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olli Manninen, Eva Ydrén, Elina Hinkkanen, * Naturskyddare, Päivi Mattila</t>
+          <t>Olli Manninen, * Naturskyddare, Eva Ydrén, Elina Hinkkanen, Päivi Mattila</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1557,37 +1448,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89592158</v>
+        <v>480417</v>
       </c>
       <c r="B9" t="n">
-        <v>56812</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102999</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1597,13 +1483,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>417978.005722511</v>
+        <v>418065</v>
       </c>
       <c r="R9" t="n">
-        <v>6899127.932719948</v>
+        <v>6899086</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1627,22 +1513,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-05-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-05-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,74 +1530,74 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Möjligen flyttande</t>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Olli Manninen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Olli Manninen, Eva Ydrén, Elina Hinkkanen, * Naturskyddare, Päivi Mattila</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Naturskyddare</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89592164</v>
+        <v>128315496</v>
       </c>
       <c r="B10" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hovdhållan, Hjd</t>
+          <t>Svartåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>417901.8604673992</v>
+        <v>417708</v>
       </c>
       <c r="R10" t="n">
-        <v>6899071.918606599</v>
+        <v>6899754</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1748,22 +1624,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1778,31 +1654,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89592157</v>
+        <v>678651</v>
       </c>
       <c r="B11" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,21 +1677,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1834,13 +1701,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>417903.1935419039</v>
+        <v>418009</v>
       </c>
       <c r="R11" t="n">
-        <v>6899069.085923558</v>
+        <v>6899124</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1864,22 +1731,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-05-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-05-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,35 +1747,40 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Olli Manninen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Olli Manninen, Päivi Mattila, Eva Ydrén, * Naturskyddare, Elina Hinkkanen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Naturskyddare</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89592177</v>
+        <v>678658</v>
       </c>
       <c r="B12" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,21 +1788,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1950,13 +1812,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>417903.1935419039</v>
+        <v>417921</v>
       </c>
       <c r="R12" t="n">
-        <v>6899069.085923558</v>
+        <v>6899204</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1980,22 +1842,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-05-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-05-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2006,21 +1858,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Olli Manninen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Olli Manninen, Eva Ydrén, Elina Hinkkanen, * Naturskyddare, Päivi Mattila</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Naturskyddare</t>
         </is>
       </c>
     </row>
@@ -2029,16 +1891,11 @@
         <v>89592174</v>
       </c>
       <c r="B13" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2066,10 +1923,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>417971.8880438787</v>
+        <v>417972</v>
       </c>
       <c r="R13" t="n">
-        <v>6899126.214998658</v>
+        <v>6899126</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2099,19 +1956,9 @@
           <t>2020-08-28</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-08-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2142,15 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89592161</v>
+        <v>128315500</v>
       </c>
       <c r="B14" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2158,37 +2000,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hovdhållan, Hjd</t>
+          <t>Svartåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>417978.005722511</v>
+        <v>417771</v>
       </c>
       <c r="R14" t="n">
-        <v>6899127.932719948</v>
+        <v>6899716</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2212,22 +2054,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2242,26 +2084,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128315499</v>
+        <v>89592157</v>
       </c>
       <c r="B15" t="n">
-        <v>78786</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,34 +2107,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartåsvallen, Hjd</t>
+          <t>Hovdhållan, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>417746</v>
+        <v>417903</v>
       </c>
       <c r="R15" t="n">
-        <v>6899734</v>
+        <v>6899069</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2323,22 +2161,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:55</t>
+          <t>2020-08-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:55</t>
+          <t>2020-08-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2353,22 +2181,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128315500</v>
+        <v>89592161</v>
       </c>
       <c r="B16" t="n">
-        <v>92411</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2376,37 +2208,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4745</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartåsvallen, Hjd</t>
+          <t>Hovdhållan, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>417771</v>
+        <v>417978</v>
       </c>
       <c r="R16" t="n">
-        <v>6899716</v>
+        <v>6899128</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2430,22 +2262,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:57</t>
+          <t>2020-08-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:57</t>
+          <t>2020-08-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2460,22 +2282,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>128315498</v>
       </c>
       <c r="B17" t="n">
-        <v>79739</v>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2576,6 +2402,314 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>89592158</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hovdhållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>417978</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6899128</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2020-08-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2020-08-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Möjligen flyttande</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>89592177</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hovdhållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>417903</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6899069</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2020-08-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2020-08-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>89592164</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hovdhållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>417902</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6899072</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-08-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-08-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14058-2023 artfynd.xlsx
+++ b/artfynd/A 14058-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129030</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128315499</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/479998</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/480001</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/480003</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/480004</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/480412</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/480417</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1663,6 +1708,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128315496</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1774,6 +1824,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/678651</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1885,6 +1940,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/678658</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1986,6 +2046,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592174</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2093,6 +2158,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128315500</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2194,6 +2264,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592157</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2295,6 +2370,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592161</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2402,6 +2482,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128315498</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2508,6 +2593,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592158</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2609,6 +2699,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592177</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2710,8 +2805,34 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592164</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>